--- a/Data/locT_Bat_UE.xlsx
+++ b/Data/locT_Bat_UE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/alanivory34428_ufl_edu/Documents/Desktop/School/Thesis/SSS_Occupancy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="8_{44D8710D-DB49-424D-B4D7-C2725C31565F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E696A4A-3970-44FD-90B4-6558EF83BF0D}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{44D8710D-DB49-424D-B4D7-C2725C31565F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{128F851E-EAD9-4993-B23D-C54D941BB9D7}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{50502A11-8049-4347-9918-47058886ACB6}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{50502A11-8049-4347-9918-47058886ACB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet3!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="165">
   <si>
     <t>OID</t>
   </si>
@@ -531,6 +531,12 @@
   </si>
   <si>
     <t>System_Type</t>
+  </si>
+  <si>
+    <t>Mount</t>
+  </si>
+  <si>
+    <t>Magnet</t>
   </si>
 </sst>
 </file>
@@ -877,7 +883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82566BAF-EE76-4103-B0C9-33CC005E7C44}">
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
@@ -893,7 +899,7 @@
     <col min="18" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -945,8 +951,11 @@
       <c r="Q1" s="9" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R1" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>13</v>
       </c>
@@ -987,7 +996,7 @@
         <v>0.88</v>
       </c>
       <c r="N2" s="9">
-        <f>CONVERT(D2,"in","cm")</f>
+        <f t="shared" ref="N2:N21" si="0">CONVERT(D2,"in","cm")</f>
         <v>45.72</v>
       </c>
       <c r="O2" s="9">
@@ -999,8 +1008,11 @@
       <c r="Q2" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R2" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>17</v>
       </c>
@@ -1041,7 +1053,7 @@
         <v>0.4</v>
       </c>
       <c r="N3" s="9">
-        <f>CONVERT(D3,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>30.48</v>
       </c>
       <c r="O3" s="9">
@@ -1053,8 +1065,11 @@
       <c r="Q3" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R3" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>21</v>
       </c>
@@ -1095,7 +1110,7 @@
         <v>1.95</v>
       </c>
       <c r="N4" s="9">
-        <f>CONVERT(D4,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>60.96</v>
       </c>
       <c r="O4" s="9">
@@ -1107,8 +1122,11 @@
       <c r="Q4" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R4" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>23</v>
       </c>
@@ -1149,7 +1167,7 @@
         <v>0.6</v>
       </c>
       <c r="N5" s="9">
-        <f>CONVERT(D5,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>38.1</v>
       </c>
       <c r="O5" s="9">
@@ -1161,8 +1179,11 @@
       <c r="Q5" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R5" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>24</v>
       </c>
@@ -1203,7 +1224,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="N6" s="9">
-        <f>CONVERT(D6,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>45.72</v>
       </c>
       <c r="O6" s="9">
@@ -1215,8 +1236,11 @@
       <c r="Q6" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R6" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>25</v>
       </c>
@@ -1257,7 +1281,7 @@
         <v>1.22</v>
       </c>
       <c r="N7" s="9">
-        <f>CONVERT(D7,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>38.1</v>
       </c>
       <c r="O7" s="9">
@@ -1269,8 +1293,11 @@
       <c r="Q7" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R7" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>48</v>
       </c>
@@ -1311,7 +1338,7 @@
         <v>1.3</v>
       </c>
       <c r="N8" s="9">
-        <f>CONVERT(D8,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>76.2</v>
       </c>
       <c r="O8" s="9">
@@ -1323,8 +1350,11 @@
       <c r="Q8" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R8" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>51</v>
       </c>
@@ -1365,7 +1395,7 @@
         <v>0.76</v>
       </c>
       <c r="N9" s="9">
-        <f>CONVERT(D9,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>76.2</v>
       </c>
       <c r="O9" s="9">
@@ -1377,8 +1407,11 @@
       <c r="Q9" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R9" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>52</v>
       </c>
@@ -1419,7 +1452,7 @@
         <v>1.4</v>
       </c>
       <c r="N10" s="9">
-        <f>CONVERT(D10,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>76.2</v>
       </c>
       <c r="O10" s="9">
@@ -1431,8 +1464,11 @@
       <c r="Q10" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R10" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>53</v>
       </c>
@@ -1473,7 +1509,7 @@
         <v>1.35</v>
       </c>
       <c r="N11" s="9">
-        <f>CONVERT(D11,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>106.67999999999999</v>
       </c>
       <c r="O11" s="9">
@@ -1485,8 +1521,11 @@
       <c r="Q11" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R11" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>54</v>
       </c>
@@ -1527,7 +1566,7 @@
         <v>1.36</v>
       </c>
       <c r="N12" s="9">
-        <f>CONVERT(D12,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>45.72</v>
       </c>
       <c r="O12" s="9">
@@ -1539,8 +1578,11 @@
       <c r="Q12" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R12" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>57</v>
       </c>
@@ -1581,7 +1623,7 @@
         <v>0.88</v>
       </c>
       <c r="N13" s="9">
-        <f>CONVERT(D13,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>60.96</v>
       </c>
       <c r="O13" s="9">
@@ -1593,8 +1635,11 @@
       <c r="Q13" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R13" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>59</v>
       </c>
@@ -1635,7 +1680,7 @@
         <v>2.39</v>
       </c>
       <c r="N14" s="9">
-        <f>CONVERT(D14,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>76.2</v>
       </c>
       <c r="O14" s="9">
@@ -1647,8 +1692,11 @@
       <c r="Q14" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R14" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>60</v>
       </c>
@@ -1689,7 +1737,7 @@
         <v>1.8</v>
       </c>
       <c r="N15" s="9">
-        <f>CONVERT(D15,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>76.2</v>
       </c>
       <c r="O15" s="9">
@@ -1701,8 +1749,11 @@
       <c r="Q15" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R15" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>67</v>
       </c>
@@ -1743,7 +1794,7 @@
         <v>2.0699999999999998</v>
       </c>
       <c r="N16" s="9">
-        <f>CONVERT(D16,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>91.44</v>
       </c>
       <c r="O16" s="9">
@@ -1755,8 +1806,11 @@
       <c r="Q16" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R16" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>68</v>
       </c>
@@ -1797,7 +1851,7 @@
         <v>1.3</v>
       </c>
       <c r="N17" s="9">
-        <f>CONVERT(D17,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>60.96</v>
       </c>
       <c r="O17" s="9">
@@ -1809,8 +1863,11 @@
       <c r="Q17" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R17" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>71</v>
       </c>
@@ -1851,7 +1908,7 @@
         <v>0.93</v>
       </c>
       <c r="N18" s="9">
-        <f>CONVERT(D18,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>38.1</v>
       </c>
       <c r="O18" s="9">
@@ -1863,8 +1920,11 @@
       <c r="Q18" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R18" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>72</v>
       </c>
@@ -1905,7 +1965,7 @@
         <v>1.68</v>
       </c>
       <c r="N19" s="9">
-        <f>CONVERT(D19,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>60.96</v>
       </c>
       <c r="O19" s="9">
@@ -1917,8 +1977,11 @@
       <c r="Q19" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R19" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>75</v>
       </c>
@@ -1959,7 +2022,7 @@
         <v>1.81</v>
       </c>
       <c r="N20" s="9">
-        <f>CONVERT(D20,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>96.52</v>
       </c>
       <c r="O20" s="9">
@@ -1971,8 +2034,11 @@
       <c r="Q20" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R20" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>76</v>
       </c>
@@ -2013,7 +2079,7 @@
         <v>1.8</v>
       </c>
       <c r="N21" s="9">
-        <f>CONVERT(D21,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>38.1</v>
       </c>
       <c r="O21" s="9">
@@ -2025,8 +2091,11 @@
       <c r="Q21" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R21" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>79</v>
       </c>
@@ -2078,8 +2147,11 @@
       <c r="Q22" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R22" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>84</v>
       </c>
@@ -2132,8 +2204,11 @@
       <c r="Q23" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R23" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>85</v>
       </c>
@@ -2186,8 +2261,11 @@
       <c r="Q24" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R24" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>86</v>
       </c>
@@ -2240,8 +2318,11 @@
       <c r="Q25" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R25" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>89</v>
       </c>
@@ -2293,8 +2374,11 @@
       <c r="Q26" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R26" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>90</v>
       </c>
@@ -2335,7 +2419,7 @@
         <v>2</v>
       </c>
       <c r="N27" s="9">
-        <f>CONVERT(D27,"in","cm")</f>
+        <f t="shared" ref="N27:N34" si="1">CONVERT(D27,"in","cm")</f>
         <v>76.2</v>
       </c>
       <c r="O27" s="9">
@@ -2347,8 +2431,11 @@
       <c r="Q27" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R27" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>91</v>
       </c>
@@ -2389,7 +2476,7 @@
         <v>2.6</v>
       </c>
       <c r="N28" s="9">
-        <f>CONVERT(D28,"in","cm")</f>
+        <f t="shared" si="1"/>
         <v>182.88</v>
       </c>
       <c r="O28" s="9">
@@ -2401,8 +2488,11 @@
       <c r="Q28" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R28" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>92</v>
       </c>
@@ -2443,7 +2533,7 @@
         <v>0.68</v>
       </c>
       <c r="N29" s="9">
-        <f>CONVERT(D29,"in","cm")</f>
+        <f t="shared" si="1"/>
         <v>38.1</v>
       </c>
       <c r="O29" s="9">
@@ -2455,8 +2545,11 @@
       <c r="Q29" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R29" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>94</v>
       </c>
@@ -2497,7 +2590,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="N30" s="9">
-        <f>CONVERT(D30,"in","cm")</f>
+        <f t="shared" si="1"/>
         <v>152.4</v>
       </c>
       <c r="O30" s="9">
@@ -2509,8 +2602,11 @@
       <c r="Q30" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R30" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>95</v>
       </c>
@@ -2551,7 +2647,7 @@
         <v>1.25</v>
       </c>
       <c r="N31" s="9">
-        <f>CONVERT(D31,"in","cm")</f>
+        <f t="shared" si="1"/>
         <v>60.96</v>
       </c>
       <c r="O31" s="9">
@@ -2563,8 +2659,11 @@
       <c r="Q31" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R31" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>170</v>
       </c>
@@ -2605,7 +2704,7 @@
         <v>0.5</v>
       </c>
       <c r="N32" s="9">
-        <f>CONVERT(D32,"in","cm")</f>
+        <f t="shared" si="1"/>
         <v>60.96</v>
       </c>
       <c r="O32" s="9">
@@ -2617,8 +2716,11 @@
       <c r="Q32" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R32" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
         <v>220</v>
       </c>
@@ -2659,7 +2761,7 @@
         <v>2.1</v>
       </c>
       <c r="N33" s="9">
-        <f>CONVERT(D33,"in","cm")</f>
+        <f t="shared" si="1"/>
         <v>60.96</v>
       </c>
       <c r="O33" s="9">
@@ -2671,8 +2773,11 @@
       <c r="Q33" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R33" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>300</v>
       </c>
@@ -2713,7 +2818,7 @@
         <v>2.4</v>
       </c>
       <c r="N34" s="9">
-        <f>CONVERT(D34,"in","cm")</f>
+        <f t="shared" si="1"/>
         <v>91.44</v>
       </c>
       <c r="O34" s="9">
@@ -2725,13 +2830,12 @@
       <c r="Q34" s="9" t="s">
         <v>160</v>
       </c>
+      <c r="R34" s="9" t="s">
+        <v>164</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1" xr:uid="{82566BAF-EE76-4103-B0C9-33CC005E7C44}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q34">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:R1" xr:uid="{82566BAF-EE76-4103-B0C9-33CC005E7C44}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
